--- a/作业反馈/ASP作业提交情况.xlsx
+++ b/作业反馈/ASP作业提交情况.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surface\Documents\Sync\Teaching\本学期\选课名单\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surface\Documents\GitHub\ASP.NET\作业反馈\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1419,7 +1419,9 @@
       <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -1533,7 +1535,9 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -1647,7 +1651,9 @@
       <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -1761,7 +1767,9 @@
       <c r="F6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="2"/>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -1875,7 +1883,9 @@
       <c r="F7" s="2">
         <v>1</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -1989,7 +1999,9 @@
       <c r="F8" s="2">
         <v>1</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -2103,7 +2115,9 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -2217,7 +2231,9 @@
       <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -2331,7 +2347,9 @@
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -2445,7 +2463,9 @@
       <c r="F12" s="2">
         <v>0</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -2559,7 +2579,9 @@
       <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -2673,7 +2695,9 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="2"/>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -2787,7 +2811,9 @@
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -2901,7 +2927,9 @@
       <c r="F16" s="2">
         <v>1</v>
       </c>
-      <c r="G16" s="2"/>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3015,7 +3043,9 @@
       <c r="F17" s="2">
         <v>1</v>
       </c>
-      <c r="G17" s="2"/>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3129,7 +3159,9 @@
       <c r="F18" s="2">
         <v>1</v>
       </c>
-      <c r="G18" s="2"/>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3243,7 +3275,9 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="G19" s="2"/>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -3357,7 +3391,9 @@
       <c r="F20" s="2">
         <v>1</v>
       </c>
-      <c r="G20" s="2"/>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -3471,7 +3507,9 @@
       <c r="F21" s="2">
         <v>1</v>
       </c>
-      <c r="G21" s="2"/>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -3585,7 +3623,9 @@
       <c r="F22" s="2">
         <v>1</v>
       </c>
-      <c r="G22" s="2"/>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -3699,7 +3739,9 @@
       <c r="F23" s="2">
         <v>1</v>
       </c>
-      <c r="G23" s="2"/>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -3813,7 +3855,9 @@
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="2"/>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -3927,7 +3971,9 @@
       <c r="F25" s="2">
         <v>1</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -4041,7 +4087,9 @@
       <c r="F26" s="2">
         <v>1</v>
       </c>
-      <c r="G26" s="2"/>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -4155,7 +4203,9 @@
       <c r="F27" s="2">
         <v>1</v>
       </c>
-      <c r="G27" s="2"/>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -4269,7 +4319,9 @@
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="2"/>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -4383,7 +4435,9 @@
       <c r="F29" s="2">
         <v>1</v>
       </c>
-      <c r="G29" s="2"/>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -4497,7 +4551,9 @@
       <c r="F30" s="2">
         <v>1</v>
       </c>
-      <c r="G30" s="2"/>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -4611,7 +4667,9 @@
       <c r="F31" s="2">
         <v>1</v>
       </c>
-      <c r="G31" s="2"/>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -4725,7 +4783,9 @@
       <c r="F32" s="2">
         <v>1</v>
       </c>
-      <c r="G32" s="2"/>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -4839,7 +4899,9 @@
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="2"/>
+      <c r="G33" s="2">
+        <v>0</v>
+      </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -4953,7 +5015,9 @@
       <c r="F34" s="2">
         <v>1</v>
       </c>
-      <c r="G34" s="2"/>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
@@ -5067,7 +5131,9 @@
       <c r="F35" s="2">
         <v>1</v>
       </c>
-      <c r="G35" s="2"/>
+      <c r="G35" s="2">
+        <v>1</v>
+      </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -5181,7 +5247,9 @@
       <c r="F36" s="2">
         <v>1</v>
       </c>
-      <c r="G36" s="2"/>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
@@ -5295,7 +5363,9 @@
       <c r="F37" s="2">
         <v>1</v>
       </c>
-      <c r="G37" s="2"/>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
@@ -5409,7 +5479,9 @@
       <c r="F38" s="2">
         <v>1</v>
       </c>
-      <c r="G38" s="2"/>
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
@@ -5523,7 +5595,9 @@
       <c r="F39" s="2">
         <v>1</v>
       </c>
-      <c r="G39" s="2"/>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
@@ -5637,7 +5711,9 @@
       <c r="F40" s="2">
         <v>1</v>
       </c>
-      <c r="G40" s="2"/>
+      <c r="G40" s="2">
+        <v>1</v>
+      </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
@@ -5751,7 +5827,9 @@
       <c r="F41" s="2">
         <v>1</v>
       </c>
-      <c r="G41" s="2"/>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
@@ -5865,7 +5943,9 @@
       <c r="F42" s="2">
         <v>1</v>
       </c>
-      <c r="G42" s="2"/>
+      <c r="G42" s="2">
+        <v>1</v>
+      </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
@@ -5979,7 +6059,9 @@
       <c r="F43" s="2">
         <v>1</v>
       </c>
-      <c r="G43" s="2"/>
+      <c r="G43" s="2">
+        <v>1</v>
+      </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
@@ -6093,7 +6175,9 @@
       <c r="F44" s="2">
         <v>0</v>
       </c>
-      <c r="G44" s="2"/>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -6207,7 +6291,9 @@
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="2"/>
+      <c r="G45" s="2">
+        <v>1</v>
+      </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -6321,7 +6407,9 @@
       <c r="F46" s="2">
         <v>1</v>
       </c>
-      <c r="G46" s="2"/>
+      <c r="G46" s="2">
+        <v>1</v>
+      </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -6435,7 +6523,9 @@
       <c r="F47" s="2">
         <v>1</v>
       </c>
-      <c r="G47" s="2"/>
+      <c r="G47" s="2">
+        <v>11</v>
+      </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -6549,7 +6639,9 @@
       <c r="F48" s="2">
         <v>1</v>
       </c>
-      <c r="G48" s="2"/>
+      <c r="G48" s="2">
+        <v>1</v>
+      </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
@@ -6663,7 +6755,9 @@
       <c r="F49" s="2">
         <v>1</v>
       </c>
-      <c r="G49" s="2"/>
+      <c r="G49" s="2">
+        <v>1</v>
+      </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
@@ -6777,7 +6871,9 @@
       <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="2"/>
+      <c r="G50" s="2">
+        <v>1</v>
+      </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -6891,7 +6987,9 @@
       <c r="F51" s="2">
         <v>1</v>
       </c>
-      <c r="G51" s="2"/>
+      <c r="G51" s="2">
+        <v>1</v>
+      </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -7005,7 +7103,9 @@
       <c r="F52" s="2">
         <v>0</v>
       </c>
-      <c r="G52" s="2"/>
+      <c r="G52" s="2">
+        <v>0</v>
+      </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -7119,7 +7219,9 @@
       <c r="F53" s="2">
         <v>0</v>
       </c>
-      <c r="G53" s="2"/>
+      <c r="G53" s="2">
+        <v>1</v>
+      </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -7233,7 +7335,9 @@
       <c r="F54" s="2">
         <v>1</v>
       </c>
-      <c r="G54" s="2"/>
+      <c r="G54" s="2">
+        <v>1</v>
+      </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -7347,7 +7451,9 @@
       <c r="F55" s="2">
         <v>1</v>
       </c>
-      <c r="G55" s="2"/>
+      <c r="G55" s="2">
+        <v>1</v>
+      </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -7461,7 +7567,9 @@
       <c r="F56" s="2">
         <v>1</v>
       </c>
-      <c r="G56" s="2"/>
+      <c r="G56" s="2">
+        <v>1</v>
+      </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -7575,7 +7683,9 @@
       <c r="F57" s="2">
         <v>1</v>
       </c>
-      <c r="G57" s="2"/>
+      <c r="G57" s="2">
+        <v>1</v>
+      </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -7689,7 +7799,9 @@
       <c r="F58" s="2">
         <v>0</v>
       </c>
-      <c r="G58" s="2"/>
+      <c r="G58" s="2">
+        <v>1</v>
+      </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -7803,7 +7915,9 @@
       <c r="F59" s="2">
         <v>1</v>
       </c>
-      <c r="G59" s="2"/>
+      <c r="G59" s="2">
+        <v>1</v>
+      </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -7917,7 +8031,9 @@
       <c r="F60" s="2">
         <v>1</v>
       </c>
-      <c r="G60" s="2"/>
+      <c r="G60" s="2">
+        <v>1</v>
+      </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -8031,7 +8147,9 @@
       <c r="F61" s="2">
         <v>0</v>
       </c>
-      <c r="G61" s="2"/>
+      <c r="G61" s="2">
+        <v>1</v>
+      </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -8145,7 +8263,9 @@
       <c r="F62" s="2">
         <v>1</v>
       </c>
-      <c r="G62" s="2"/>
+      <c r="G62" s="2">
+        <v>1</v>
+      </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -8259,7 +8379,9 @@
       <c r="F63" s="2">
         <v>1</v>
       </c>
-      <c r="G63" s="2"/>
+      <c r="G63" s="2">
+        <v>1</v>
+      </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -8373,7 +8495,9 @@
       <c r="F64" s="2">
         <v>1</v>
       </c>
-      <c r="G64" s="2"/>
+      <c r="G64" s="2">
+        <v>1</v>
+      </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -8487,7 +8611,9 @@
       <c r="F65" s="2">
         <v>1</v>
       </c>
-      <c r="G65" s="2"/>
+      <c r="G65" s="2">
+        <v>1</v>
+      </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -8601,7 +8727,9 @@
       <c r="F66" s="2">
         <v>0</v>
       </c>
-      <c r="G66" s="2"/>
+      <c r="G66" s="2">
+        <v>0</v>
+      </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
@@ -8715,7 +8843,9 @@
       <c r="F67" s="2">
         <v>1</v>
       </c>
-      <c r="G67" s="2"/>
+      <c r="G67" s="2">
+        <v>1</v>
+      </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
@@ -8829,7 +8959,9 @@
       <c r="F68" s="2">
         <v>1</v>
       </c>
-      <c r="G68" s="2"/>
+      <c r="G68" s="2">
+        <v>1</v>
+      </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -8943,7 +9075,9 @@
       <c r="F69" s="2">
         <v>0</v>
       </c>
-      <c r="G69" s="2"/>
+      <c r="G69" s="2">
+        <v>0</v>
+      </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -9057,7 +9191,9 @@
       <c r="F70" s="2">
         <v>1</v>
       </c>
-      <c r="G70" s="2"/>
+      <c r="G70" s="2">
+        <v>1</v>
+      </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -9171,7 +9307,9 @@
       <c r="F71" s="2">
         <v>1</v>
       </c>
-      <c r="G71" s="2"/>
+      <c r="G71" s="2">
+        <v>1</v>
+      </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -9285,7 +9423,9 @@
       <c r="F72" s="2">
         <v>1</v>
       </c>
-      <c r="G72" s="2"/>
+      <c r="G72" s="2">
+        <v>1</v>
+      </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -9399,7 +9539,9 @@
       <c r="F73" s="2">
         <v>0</v>
       </c>
-      <c r="G73" s="2"/>
+      <c r="G73" s="2">
+        <v>0</v>
+      </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
